--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106483</v>
+        <v>106486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>136177598</v>
       </c>
       <c r="B8" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136177764</v>
       </c>
       <c r="B9" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>136177861</v>
       </c>
       <c r="B10" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>136177912</v>
       </c>
       <c r="B11" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>136178025</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>136178034</v>
       </c>
       <c r="B13" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>136178080</v>
       </c>
       <c r="B14" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136178091</v>
       </c>
       <c r="B15" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>136177673</v>
       </c>
       <c r="B19" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>136177709</v>
       </c>
       <c r="B21" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106487</v>
+        <v>106492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136178012</v>
       </c>
       <c r="B2" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136177941</v>
       </c>
       <c r="B3" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136177627</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136178073</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136177791</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>136177610</v>
       </c>
       <c r="B29" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136178012</v>
+        <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511223</v>
+        <v>511324</v>
       </c>
       <c r="R2" t="n">
-        <v>6511710</v>
+        <v>6511751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,38 +780,38 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136178012</t>
+          <t>https://artportalen.se/Sighting/136879938</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136177941</v>
+        <v>136178012</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>91889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>511256</v>
+        <v>511223</v>
       </c>
       <c r="R3" t="n">
-        <v>6511697</v>
+        <v>6511710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,16 +886,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177941</t>
+          <t>https://artportalen.se/Sighting/136178012</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136177627</v>
+        <v>136177941</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>511402</v>
+        <v>511256</v>
       </c>
       <c r="R4" t="n">
-        <v>6511621</v>
+        <v>6511697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,13 +992,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177627</t>
+          <t>https://artportalen.se/Sighting/136177941</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136178073</v>
+        <v>136177627</v>
       </c>
       <c r="B5" t="n">
         <v>93411</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511252</v>
+        <v>511402</v>
       </c>
       <c r="R5" t="n">
-        <v>6511767</v>
+        <v>6511621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,16 +1098,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136178073</t>
+          <t>https://artportalen.se/Sighting/136177627</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136177791</v>
+        <v>136178073</v>
       </c>
       <c r="B6" t="n">
-        <v>92134</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511336</v>
+        <v>511252</v>
       </c>
       <c r="R6" t="n">
-        <v>6511711</v>
+        <v>6511767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,11 +1180,6 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färskt bohål under fruktkropp.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1209,52 +1204,43 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177791</t>
+          <t>https://artportalen.se/Sighting/136178073</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134923529</v>
+        <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>89320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4404</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,13 +1248,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511375</v>
+        <v>511310</v>
       </c>
       <c r="R7" t="n">
-        <v>6511719</v>
+        <v>6511801</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,22 +1278,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,65 +1292,61 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134923529</t>
+          <t>https://artportalen.se/Sighting/136879552</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136177598</v>
+        <v>136177791</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>92134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>511399</v>
+        <v>511336</v>
       </c>
       <c r="R8" t="n">
-        <v>6511604</v>
+        <v>6511711</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,12 +1392,18 @@
           <t>2026-08-27</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färskt bohål under fruktkropp.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1443,48 +1421,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177598</t>
+          <t>https://artportalen.se/Sighting/136177791</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136177764</v>
+        <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>93437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1492,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>511344</v>
+        <v>511259</v>
       </c>
       <c r="R9" t="n">
-        <v>6511702</v>
+        <v>6511745</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,12 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,6 +1509,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1553,48 +1527,43 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177764</t>
+          <t>https://artportalen.se/Sighting/136879796</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136177861</v>
+        <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>58005</v>
+        <v>93447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1602,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511273</v>
+        <v>511237</v>
       </c>
       <c r="R10" t="n">
-        <v>6511682</v>
+        <v>6511780</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,12 +1601,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,6 +1615,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,48 +1633,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177861</t>
+          <t>https://artportalen.se/Sighting/136879523</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136177912</v>
+        <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>93447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1712,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511263</v>
+        <v>511229</v>
       </c>
       <c r="R11" t="n">
-        <v>6511701</v>
+        <v>6511767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,12 +1707,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,6 +1721,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1773,16 +1739,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177912</t>
+          <t>https://artportalen.se/Sighting/136879537</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136178025</v>
+        <v>134923529</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>57977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1807,12 +1773,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1822,13 +1792,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511198</v>
+        <v>511375</v>
       </c>
       <c r="R12" t="n">
-        <v>6511714</v>
+        <v>6511719</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,12 +1822,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,24 +1852,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Daniel Hjelm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136178025</t>
+          <t>https://artportalen.se/Sighting/134923529</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136178034</v>
+        <v>136177598</v>
       </c>
       <c r="B13" t="n">
         <v>58005</v>
@@ -1932,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>511243</v>
+        <v>511399</v>
       </c>
       <c r="R13" t="n">
-        <v>6511729</v>
+        <v>6511604</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,13 +1973,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136178034</t>
+          <t>https://artportalen.se/Sighting/136177598</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136178080</v>
+        <v>136177764</v>
       </c>
       <c r="B14" t="n">
         <v>58005</v>
@@ -2042,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>511256</v>
+        <v>511344</v>
       </c>
       <c r="R14" t="n">
-        <v>6511775</v>
+        <v>6511702</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,13 +2083,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136178080</t>
+          <t>https://artportalen.se/Sighting/136177764</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136178091</v>
+        <v>136177861</v>
       </c>
       <c r="B15" t="n">
         <v>58005</v>
@@ -2152,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>511235</v>
+        <v>511273</v>
       </c>
       <c r="R15" t="n">
-        <v>6511768</v>
+        <v>6511682</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,54 +2193,46 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136178091</t>
+          <t>https://artportalen.se/Sighting/136177861</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134922927</v>
+        <v>136177912</v>
       </c>
       <c r="B16" t="n">
-        <v>58415</v>
+        <v>58005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2270,13 +2242,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>511395</v>
+        <v>511263</v>
       </c>
       <c r="R16" t="n">
-        <v>6511620</v>
+        <v>6511701</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,22 +2272,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,61 +2292,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922927</t>
+          <t>https://artportalen.se/Sighting/136177912</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134922217</v>
+        <v>136178025</v>
       </c>
       <c r="B17" t="n">
-        <v>58141</v>
+        <v>58005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2394,13 +2352,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511217</v>
+        <v>511198</v>
       </c>
       <c r="R17" t="n">
-        <v>6511696</v>
+        <v>6511714</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2424,22 +2382,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2454,61 +2402,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922217</t>
+          <t>https://artportalen.se/Sighting/136178025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134923530</v>
+        <v>136178034</v>
       </c>
       <c r="B18" t="n">
-        <v>58141</v>
+        <v>58005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2518,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>511375</v>
+        <v>511243</v>
       </c>
       <c r="R18" t="n">
-        <v>6511719</v>
+        <v>6511729</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2548,22 +2492,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,49 +2512,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134923530</t>
+          <t>https://artportalen.se/Sighting/136178034</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136177673</v>
+        <v>136178080</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2628,7 +2562,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2638,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>511363</v>
+        <v>511256</v>
       </c>
       <c r="R19" t="n">
-        <v>6511641</v>
+        <v>6511775</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,16 +2633,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177673</t>
+          <t>https://artportalen.se/Sighting/136178080</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134922216</v>
+        <v>136178091</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,16 +2650,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2733,16 +2667,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2752,13 +2682,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>511217</v>
+        <v>511235</v>
       </c>
       <c r="R20" t="n">
-        <v>6511696</v>
+        <v>6511768</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2782,22 +2712,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,27 +2732,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922216</t>
+          <t>https://artportalen.se/Sighting/136178091</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136177709</v>
+        <v>136879583</v>
       </c>
       <c r="B21" t="n">
-        <v>58164</v>
+        <v>58005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2840,16 +2760,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103023</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2862,7 +2782,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2872,13 +2792,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511343</v>
+        <v>511288</v>
       </c>
       <c r="R21" t="n">
-        <v>6511686</v>
+        <v>6511780</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,12 +2822,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2933,38 +2853,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177709</t>
+          <t>https://artportalen.se/Sighting/136879583</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134922543</v>
+        <v>136880102</v>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>5181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>102204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2973,7 +2893,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2983,13 +2903,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>511217</v>
+        <v>511409</v>
       </c>
       <c r="R22" t="n">
-        <v>6511651</v>
+        <v>6511616</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3013,22 +2933,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,33 +2947,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922543</t>
+          <t>https://artportalen.se/Sighting/136880102</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134923659</v>
+        <v>134922927</v>
       </c>
       <c r="B23" t="n">
-        <v>61536</v>
+        <v>58415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3071,34 +2982,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106670</v>
+        <v>103001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart skogssnigel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arion ater ater</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>pulli/nyligen flygga ungar</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3108,13 +3022,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>511339</v>
+        <v>511395</v>
       </c>
       <c r="R23" t="n">
-        <v>6511743</v>
+        <v>6511620</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3143,7 +3057,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3153,7 +3067,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3179,16 +3093,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134923659</t>
+          <t>https://artportalen.se/Sighting/134922927</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134922213</v>
+        <v>134922217</v>
       </c>
       <c r="B24" t="n">
-        <v>56711</v>
+        <v>58141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,33 +3110,33 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206046</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3303,38 +3217,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922213</t>
+          <t>https://artportalen.se/Sighting/134922217</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134922396</v>
+        <v>134923530</v>
       </c>
       <c r="B25" t="n">
-        <v>58844</v>
+        <v>58141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3342,10 +3256,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3353,13 +3270,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511214</v>
+        <v>511375</v>
       </c>
       <c r="R25" t="n">
-        <v>6511665</v>
+        <v>6511719</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,7 +3305,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3315,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,52 +3341,48 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922396</t>
+          <t>https://artportalen.se/Sighting/134923530</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134922398</v>
+        <v>136177673</v>
       </c>
       <c r="B26" t="n">
-        <v>99159</v>
+        <v>58169</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3477,13 +3390,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511214</v>
+        <v>511363</v>
       </c>
       <c r="R26" t="n">
-        <v>6511665</v>
+        <v>6511641</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3507,22 +3420,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:38</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,27 +3440,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Daniel Hjelm</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922398</t>
+          <t>https://artportalen.se/Sighting/136177673</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134922931</v>
+        <v>134922216</v>
       </c>
       <c r="B27" t="n">
-        <v>111210</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3565,27 +3468,35 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220240</v>
+        <v>103023</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3593,13 +3504,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>511359</v>
+        <v>511217</v>
       </c>
       <c r="R27" t="n">
-        <v>6511577</v>
+        <v>6511696</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3628,7 +3539,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3549,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3664,54 +3575,62 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134922931</t>
+          <t>https://artportalen.se/Sighting/134922216</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>116161227</v>
+        <v>136177709</v>
       </c>
       <c r="B28" t="n">
-        <v>99118</v>
+        <v>58164</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillsjökärret, Ög</t>
+          <t>Nycklekärret, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>511259</v>
+        <v>511343</v>
       </c>
       <c r="R28" t="n">
-        <v>6511768</v>
+        <v>6511686</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,12 +3654,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,27 +3674,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116161227</t>
+          <t>https://artportalen.se/Sighting/136177709</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136177610</v>
+        <v>136879510</v>
       </c>
       <c r="B29" t="n">
-        <v>106494</v>
+        <v>5202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3783,27 +3702,32 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3811,10 +3735,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511400</v>
+        <v>511237</v>
       </c>
       <c r="R29" t="n">
-        <v>6511614</v>
+        <v>6511692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3841,12 +3765,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3873,16 +3797,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136177610</t>
+          <t>https://artportalen.se/Sighting/136879510</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134921808</v>
+        <v>134922543</v>
       </c>
       <c r="B30" t="n">
-        <v>100854</v>
+        <v>8450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3890,27 +3814,32 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222584</v>
+        <v>106554</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3918,13 +3847,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511153</v>
+        <v>511217</v>
       </c>
       <c r="R30" t="n">
-        <v>6511567</v>
+        <v>6511651</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3953,7 +3882,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3963,7 +3892,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,44 +3918,53 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134921808</t>
+          <t>https://artportalen.se/Sighting/134922543</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134922928</v>
+        <v>134923659</v>
       </c>
       <c r="B31" t="n">
-        <v>99519</v>
+        <v>61536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222812</v>
+        <v>106670</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4034,13 +3972,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>511359</v>
+        <v>511339</v>
       </c>
       <c r="R31" t="n">
-        <v>6511577</v>
+        <v>6511743</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4069,7 +4007,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4079,7 +4017,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4104,6 +4042,1146 @@
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134923659</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134922213</v>
+      </c>
+      <c r="B32" t="n">
+        <v>56711</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>511217</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6511696</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922213</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134922396</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58844</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>511214</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6511665</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922396</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134922398</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>511214</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6511665</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922398</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134922931</v>
+      </c>
+      <c r="B35" t="n">
+        <v>111210</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>511359</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6511577</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134922931</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>116161227</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lillsjökärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>511259</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6511768</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116161227</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136177610</v>
+      </c>
+      <c r="B37" t="n">
+        <v>106494</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>511400</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6511614</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136177610</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136879875</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106494</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>511321</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6511766</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136879875</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136879531</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98218</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>511229</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6511774</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136879531</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134921808</v>
+      </c>
+      <c r="B40" t="n">
+        <v>100854</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>511153</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6511567</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134921808</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134922928</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99519</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nycklekärret, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>511359</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6511577</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Hjelm</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134922928</t>
         </is>
@@ -4141,6 +5219,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98226</v>
+        <v>98227</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98227</v>
+        <v>98233</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89331</v>
+        <v>89335</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98233</v>
+        <v>98237</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98237</v>
+        <v>98239</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89335</v>
+        <v>89337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98239</v>
+        <v>98241</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89337</v>
+        <v>89350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136879583</v>
       </c>
       <c r="B21" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98241</v>
+        <v>98254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89350</v>
+        <v>89352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136879583</v>
       </c>
       <c r="B21" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98254</v>
+        <v>98256</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -2780,11 +2780,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2891,11 +2887,7 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3723,11 +3715,7 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98256</v>
+        <v>98259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89355</v>
+        <v>89365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136879583</v>
       </c>
       <c r="B21" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>136880102</v>
       </c>
       <c r="B22" t="n">
-        <v>5181</v>
+        <v>5187</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>136879510</v>
       </c>
       <c r="B29" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89365</v>
+        <v>89366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89366</v>
+        <v>89369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136879583</v>
       </c>
       <c r="B21" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89369</v>
+        <v>89374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>136879583</v>
       </c>
       <c r="B21" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89374</v>
+        <v>89385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 23975-2026 artfynd.xlsx
+++ b/artfynd/A 23975-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136879938</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136879552</v>
       </c>
       <c r="B7" t="n">
-        <v>89385</v>
+        <v>89386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136879796</v>
       </c>
       <c r="B9" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136879523</v>
       </c>
       <c r="B10" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>136879537</v>
       </c>
       <c r="B11" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>136879875</v>
       </c>
       <c r="B38" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>136879531</v>
       </c>
       <c r="B39" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
